--- a/assets/veille/Tab2Synthèse.xlsx
+++ b/assets/veille/Tab2Synthèse.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Verand NGUIE\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Verand NGUIE\Documents\CDT LIBRE\Portfolio\verand-nj.github.io\assets\veille\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BA56D3B-0D73-46B3-8F29-FB3D8CC587A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EF93B1E-ABDA-4C0D-A6BC-1B3E9F0EC02C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1440" yWindow="1188" windowWidth="21600" windowHeight="11772" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tableau de synthèse Épreuve E4" sheetId="1" r:id="rId1"/>
@@ -174,9 +174,6 @@
     <t>Gestion et administration d'un Actif Diretory</t>
   </si>
   <si>
-    <t>Configuration Windows Serveur 2019</t>
-  </si>
-  <si>
     <t>Gestion et aAdministration sous Linux</t>
   </si>
   <si>
@@ -205,6 +202,9 @@
   </si>
   <si>
     <t>Adresse URL du portfolio : https://verand-nj.github.io</t>
+  </si>
+  <si>
+    <t>Configuration Windows Serveur 2022</t>
   </si>
 </sst>
 </file>
@@ -748,15 +748,39 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -788,30 +812,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1133,56 +1133,56 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25" t="s">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="H1" s="25"/>
+      <c r="H1" s="23"/>
     </row>
     <row r="2" spans="1:43" ht="41.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
     </row>
     <row r="3" spans="1:43" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="37" t="s">
+      <c r="A3" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="B3" s="38"/>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="39"/>
-      <c r="F3" s="43" t="s">
-        <v>46</v>
-      </c>
-      <c r="G3" s="38"/>
-      <c r="H3" s="44"/>
+      <c r="B3" s="25"/>
+      <c r="C3" s="25"/>
+      <c r="D3" s="25"/>
+      <c r="E3" s="26"/>
+      <c r="F3" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="G3" s="25"/>
+      <c r="H3" s="31"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
     <row r="4" spans="1:43" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="40" t="s">
-        <v>47</v>
-      </c>
-      <c r="B4" s="41"/>
-      <c r="C4" s="41"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="42"/>
+      <c r="A4" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" s="28"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="29"/>
       <c r="F4" s="12" t="s">
         <v>2</v>
       </c>
@@ -1194,22 +1194,22 @@
       </c>
     </row>
     <row r="5" spans="1:43" ht="40.049999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="34" t="s">
-        <v>48</v>
-      </c>
-      <c r="B5" s="35"/>
-      <c r="C5" s="35"/>
-      <c r="D5" s="35"/>
-      <c r="E5" s="35"/>
-      <c r="F5" s="35"/>
-      <c r="G5" s="35"/>
-      <c r="H5" s="36"/>
+      <c r="A5" s="42" t="s">
+        <v>47</v>
+      </c>
+      <c r="B5" s="43"/>
+      <c r="C5" s="43"/>
+      <c r="D5" s="43"/>
+      <c r="E5" s="43"/>
+      <c r="F5" s="43"/>
+      <c r="G5" s="43"/>
+      <c r="H5" s="44"/>
     </row>
     <row r="6" spans="1:43" ht="90" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="32" t="s">
+      <c r="B6" s="40" t="s">
         <v>5</v>
       </c>
       <c r="C6" s="6" t="s">
@@ -1232,8 +1232,8 @@
       </c>
     </row>
     <row r="7" spans="1:43" s="2" customFormat="1" ht="325.05" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="24"/>
-      <c r="B7" s="33"/>
+      <c r="A7" s="33"/>
+      <c r="B7" s="41"/>
       <c r="C7" s="15" t="s">
         <v>12</v>
       </c>
@@ -1289,16 +1289,16 @@
       <c r="AQ7"/>
     </row>
     <row r="8" spans="1:43" s="2" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A8" s="26" t="s">
+      <c r="A8" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="27"/>
-      <c r="C8" s="27"/>
-      <c r="D8" s="27"/>
-      <c r="E8" s="27"/>
-      <c r="F8" s="27"/>
-      <c r="G8" s="27"/>
-      <c r="H8" s="28"/>
+      <c r="B8" s="35"/>
+      <c r="C8" s="35"/>
+      <c r="D8" s="35"/>
+      <c r="E8" s="35"/>
+      <c r="F8" s="35"/>
+      <c r="G8" s="35"/>
+      <c r="H8" s="36"/>
       <c r="I8"/>
       <c r="J8"/>
       <c r="K8"/>
@@ -1393,7 +1393,7 @@
         <v>34</v>
       </c>
       <c r="B10" s="17">
-        <v>45566</v>
+        <v>46082</v>
       </c>
       <c r="C10" s="19"/>
       <c r="D10" s="19"/>
@@ -1547,7 +1547,7 @@
     </row>
     <row r="13" spans="1:43" s="2" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="B13" s="17">
         <v>45352</v>
@@ -1598,7 +1598,7 @@
     </row>
     <row r="14" spans="1:43" s="2" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B14" s="17">
         <v>45658</v>
@@ -1651,7 +1651,7 @@
     </row>
     <row r="15" spans="1:43" s="2" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B15" s="17">
         <v>45261</v>
@@ -1706,7 +1706,7 @@
     </row>
     <row r="16" spans="1:43" s="2" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B16" s="17">
         <v>45383</v>
@@ -1759,7 +1759,7 @@
     </row>
     <row r="17" spans="1:43" s="2" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="9" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B17" s="17">
         <v>45383</v>
@@ -1810,7 +1810,7 @@
     </row>
     <row r="18" spans="1:43" s="2" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B18" s="17">
         <v>45627</v>
@@ -1862,16 +1862,16 @@
       <c r="AQ18"/>
     </row>
     <row r="19" spans="1:43" s="2" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A19" s="29" t="s">
+      <c r="A19" s="37" t="s">
         <v>19</v>
       </c>
-      <c r="B19" s="30"/>
-      <c r="C19" s="30"/>
-      <c r="D19" s="30"/>
-      <c r="E19" s="30"/>
-      <c r="F19" s="30"/>
-      <c r="G19" s="30"/>
-      <c r="H19" s="31"/>
+      <c r="B19" s="38"/>
+      <c r="C19" s="38"/>
+      <c r="D19" s="38"/>
+      <c r="E19" s="38"/>
+      <c r="F19" s="38"/>
+      <c r="G19" s="38"/>
+      <c r="H19" s="39"/>
       <c r="I19"/>
       <c r="J19"/>
       <c r="K19"/>
@@ -2264,16 +2264,16 @@
       <c r="AQ26"/>
     </row>
     <row r="27" spans="1:43" s="2" customFormat="1" ht="17.399999999999999" x14ac:dyDescent="0.25">
-      <c r="A27" s="29" t="s">
+      <c r="A27" s="37" t="s">
         <v>20</v>
       </c>
-      <c r="B27" s="30"/>
-      <c r="C27" s="30"/>
-      <c r="D27" s="30"/>
-      <c r="E27" s="30"/>
-      <c r="F27" s="30"/>
-      <c r="G27" s="30"/>
-      <c r="H27" s="31"/>
+      <c r="B27" s="38"/>
+      <c r="C27" s="38"/>
+      <c r="D27" s="38"/>
+      <c r="E27" s="38"/>
+      <c r="F27" s="38"/>
+      <c r="G27" s="38"/>
+      <c r="H27" s="39"/>
       <c r="I27"/>
       <c r="J27"/>
       <c r="K27"/>
@@ -2473,7 +2473,7 @@
     </row>
     <row r="31" spans="1:43" s="2" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B31" s="17">
         <v>45689</v>
@@ -2526,7 +2526,7 @@
     </row>
     <row r="32" spans="1:43" s="2" customFormat="1" ht="40.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B32" s="17">
         <v>45689</v>
@@ -2760,11 +2760,6 @@
     <row r="81" customFormat="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F3:H3"/>
     <mergeCell ref="A6:A7"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A8:H8"/>
@@ -2772,6 +2767,11 @@
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="B6:B7"/>
     <mergeCell ref="A5:H5"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F3:H3"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
@@ -2782,15 +2782,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010080C570BE1F615245868C7859F25F136C" ma:contentTypeVersion="14" ma:contentTypeDescription="Crée un document." ma:contentTypeScope="" ma:versionID="70f5be04c7a3d3a8c110bfea3f46ceb8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="bfc87175-da37-48f3-a062-113ddd3d15ab" xmlns:ns3="f16c1a9a-2130-486e-baa2-6111c27def44" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="126cb05c355c88af2f458bea2176669e" ns2:_="" ns3:_="">
     <xsd:import namespace="bfc87175-da37-48f3-a062-113ddd3d15ab"/>
@@ -3019,6 +3010,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -3031,14 +3031,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2757608-0B9C-43E2-B3B5-CF9F5072A299}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2F471863-8A1C-4109-B4DC-821746806E0F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3057,6 +3049,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F2757608-0B9C-43E2-B3B5-CF9F5072A299}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8E647C46-BF2A-4BDD-A049-175E0E0B52DA}">
   <ds:schemaRefs>
